--- a/exports/trend_1d/DIVISLAB_full_report.xlsx
+++ b/exports/trend_1d/DIVISLAB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>6.32</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42038</v>
+        <v>42039</v>
       </c>
       <c r="H2" t="n">
-        <v>829.95</v>
+        <v>818.03</v>
       </c>
       <c r="I2" t="n">
         <v>818.0917951100621</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.11</v>
+        <v>-3.51</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="M2" t="n">
         <v>1.28</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>10.26</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42059</v>
+        <v>42060</v>
       </c>
       <c r="H3" t="n">
-        <v>843.65</v>
+        <v>872.88</v>
       </c>
       <c r="I3" t="n">
         <v>869.513283600922</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.13</v>
+        <v>-6.71</v>
       </c>
       <c r="L3" t="n">
-        <v>3.85</v>
+        <v>7.7</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.53</v>
+        <v>3.46</v>
       </c>
       <c r="O3" t="n">
         <v>-1.44</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.27</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42117</v>
+        <v>42118</v>
       </c>
       <c r="H4" t="n">
-        <v>895.38</v>
+        <v>888.05</v>
       </c>
       <c r="I4" t="n">
         <v>889.3344704766428</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K4" t="n">
-        <v>2.58</v>
+        <v>1.74</v>
       </c>
       <c r="L4" t="n">
         <v>4.67</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.6</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42184</v>
+        <v>42185</v>
       </c>
       <c r="H5" t="n">
-        <v>916.5</v>
+        <v>939.9299999999999</v>
       </c>
       <c r="I5" t="n">
         <v>938.2703519387954</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.2</v>
+        <v>-5.84</v>
       </c>
       <c r="L5" t="n">
-        <v>6.55</v>
+        <v>6.69</v>
       </c>
       <c r="M5" t="n">
         <v>1.19</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.1</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42240</v>
+        <v>42241</v>
       </c>
       <c r="H6" t="n">
-        <v>1112.4</v>
+        <v>1080.83</v>
       </c>
       <c r="I6" t="n">
         <v>1092.847919099644</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" t="n">
-        <v>18.35</v>
+        <v>14.99</v>
       </c>
       <c r="L6" t="n">
         <v>2.52</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>15.88</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42307</v>
+        <v>42310</v>
       </c>
       <c r="H7" t="n">
-        <v>1153.84</v>
+        <v>1155.95</v>
       </c>
       <c r="I7" t="n">
         <v>1155.135542918084</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.75</v>
+        <v>-6.95</v>
       </c>
       <c r="L7" t="n">
         <v>11.72</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.81</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42377</v>
+        <v>42380</v>
       </c>
       <c r="H8" t="n">
-        <v>1129.7</v>
+        <v>1099.5</v>
       </c>
       <c r="I8" t="n">
         <v>1101.257146939401</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.27</v>
+        <v>-4.88</v>
       </c>
       <c r="L8" t="n">
         <v>8.140000000000001</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.74</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42480</v>
+        <v>42481</v>
       </c>
       <c r="H9" t="n">
-        <v>1048.55</v>
+        <v>1091.05</v>
       </c>
       <c r="I9" t="n">
         <v>1055.793130035613</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K9" t="n">
-        <v>4.63</v>
+        <v>0.77</v>
       </c>
       <c r="L9" t="n">
         <v>5.62</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.46</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42653</v>
+        <v>42656</v>
       </c>
       <c r="H10" t="n">
-        <v>1264.65</v>
+        <v>1246.5</v>
       </c>
       <c r="I10" t="n">
         <v>1251.957772254527</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K10" t="n">
-        <v>15.91</v>
+        <v>14.25</v>
       </c>
       <c r="L10" t="n">
         <v>7.11</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42768</v>
+        <v>42769</v>
       </c>
       <c r="H11" t="n">
-        <v>737.65</v>
+        <v>760.35</v>
       </c>
       <c r="I11" t="n">
         <v>754.7268328007515</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K11" t="n">
-        <v>40.82</v>
+        <v>39</v>
       </c>
       <c r="L11" t="n">
         <v>4.6</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>12.01</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42814</v>
+        <v>42815</v>
       </c>
       <c r="H12" t="n">
-        <v>790.65</v>
+        <v>634.45</v>
       </c>
       <c r="I12" t="n">
         <v>720.0501050538334</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K12" t="n">
-        <v>3.99</v>
+        <v>-16.56</v>
       </c>
       <c r="L12" t="n">
-        <v>7.81</v>
+        <v>17.33</v>
       </c>
       <c r="M12" t="n">
-        <v>0.55</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>19.76</v>
       </c>
       <c r="O12" t="n">
         <v>3.08</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>21.74</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42886</v>
+        <v>42887</v>
       </c>
       <c r="H13" t="n">
-        <v>582.15</v>
+        <v>602</v>
       </c>
       <c r="I13" t="n">
         <v>596.0541883069935</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K13" t="n">
-        <v>8.24</v>
+        <v>5.11</v>
       </c>
       <c r="L13" t="n">
         <v>12.16</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>11.16</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42937</v>
+        <v>42940</v>
       </c>
       <c r="H14" t="n">
-        <v>721.25</v>
+        <v>687.9</v>
       </c>
       <c r="I14" t="n">
         <v>690.8247280017283</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K14" t="n">
-        <v>19.81</v>
+        <v>14.27</v>
       </c>
       <c r="L14" t="n">
         <v>3.19</v>
       </c>
       <c r="M14" t="n">
-        <v>0.53</v>
+        <v>4.54</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>4.62</v>
       </c>
       <c r="O14" t="n">
         <v>3.41</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>10.69</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42976</v>
+        <v>42977</v>
       </c>
       <c r="H15" t="n">
-        <v>687.45</v>
+        <v>702.6</v>
       </c>
       <c r="I15" t="n">
         <v>697.9821461005965</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.14</v>
       </c>
       <c r="L15" t="n">
-        <v>2.62</v>
+        <v>3.07</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.76</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H16" t="n">
-        <v>1043.8</v>
+        <v>1028.25</v>
       </c>
       <c r="I16" t="n">
         <v>1032.682161045733</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K16" t="n">
-        <v>48.56</v>
+        <v>46.35</v>
       </c>
       <c r="L16" t="n">
         <v>1.49</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>11.41</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43173</v>
+        <v>43174</v>
       </c>
       <c r="H17" t="n">
-        <v>1054.85</v>
+        <v>1084.55</v>
       </c>
       <c r="I17" t="n">
         <v>1073.165034460863</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.59</v>
+        <v>-5.48</v>
       </c>
       <c r="L17" t="n">
-        <v>3.89</v>
+        <v>7.57</v>
       </c>
       <c r="M17" t="n">
         <v>0.9399999999999999</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.57</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43241</v>
+        <v>43242</v>
       </c>
       <c r="H18" t="n">
-        <v>1138.55</v>
+        <v>1121.6</v>
       </c>
       <c r="I18" t="n">
         <v>1128.13148497759</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K18" t="n">
-        <v>4.98</v>
+        <v>3.42</v>
       </c>
       <c r="L18" t="n">
         <v>5.52</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43291</v>
+        <v>43292</v>
       </c>
       <c r="H19" t="n">
-        <v>1090.85</v>
+        <v>1122.2</v>
       </c>
       <c r="I19" t="n">
         <v>1115.323046893296</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K19" t="n">
-        <v>2.74</v>
+        <v>-0.05</v>
       </c>
       <c r="L19" t="n">
         <v>4.11</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.05</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43396</v>
+        <v>43397</v>
       </c>
       <c r="H20" t="n">
-        <v>1249.7</v>
+        <v>1241</v>
       </c>
       <c r="I20" t="n">
         <v>1243.104151476947</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K20" t="n">
-        <v>11.36</v>
+        <v>10.59</v>
       </c>
       <c r="L20" t="n">
         <v>7.32</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>12.24</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43399</v>
+        <v>43402</v>
       </c>
       <c r="H21" t="n">
-        <v>1255.8</v>
+        <v>1440.15</v>
       </c>
       <c r="I21" t="n">
         <v>1392.850918906511</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.19</v>
+        <v>-16.05</v>
       </c>
       <c r="L21" t="n">
-        <v>3.01</v>
+        <v>17.05</v>
       </c>
       <c r="M21" t="n">
-        <v>0.64</v>
+        <v>5.91</v>
       </c>
       <c r="N21" t="n">
-        <v>0.97</v>
+        <v>14.68</v>
       </c>
       <c r="O21" t="n">
         <v>-0.7</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>16.8</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43516</v>
+        <v>43517</v>
       </c>
       <c r="H22" t="n">
-        <v>1560.55</v>
+        <v>1550</v>
       </c>
       <c r="I22" t="n">
         <v>1559.184144992503</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K22" t="n">
-        <v>8.359999999999999</v>
+        <v>7.63</v>
       </c>
       <c r="L22" t="n">
         <v>8.01</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>9.34</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43529</v>
+        <v>43530</v>
       </c>
       <c r="H23" t="n">
-        <v>1663.7</v>
+        <v>1705.9</v>
       </c>
       <c r="I23" t="n">
         <v>1694.751876551258</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.34</v>
+        <v>-10.06</v>
       </c>
       <c r="L23" t="n">
-        <v>8.58</v>
+        <v>11.29</v>
       </c>
       <c r="M23" t="n">
         <v>0.7</v>
       </c>
       <c r="N23" t="n">
-        <v>1.9</v>
+        <v>2.54</v>
       </c>
       <c r="O23" t="n">
         <v>-0.68</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>8.67</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43598</v>
+        <v>43599</v>
       </c>
       <c r="H24" t="n">
-        <v>1625.15</v>
+        <v>1617.35</v>
       </c>
       <c r="I24" t="n">
         <v>1622.467820138804</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.73</v>
+        <v>-5.19</v>
       </c>
       <c r="L24" t="n">
-        <v>6.03</v>
+        <v>6.56</v>
       </c>
       <c r="M24" t="n">
         <v>1.45</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>7.37</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H25" t="n">
-        <v>1732.45</v>
+        <v>1765.65</v>
       </c>
       <c r="I25" t="n">
         <v>1736.506755275017</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.12</v>
+        <v>-9.17</v>
       </c>
       <c r="L25" t="n">
-        <v>7.83</v>
+        <v>9.69</v>
       </c>
       <c r="M25" t="n">
         <v>2.9</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>8.26</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H26" t="n">
-        <v>1765.65</v>
+        <v>1593.45</v>
       </c>
       <c r="I26" t="n">
         <v>1619.737314939861</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>-9.75</v>
       </c>
       <c r="L26" t="n">
-        <v>1.62</v>
+        <v>10.62</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="O26" t="n">
         <v>1.92</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>15</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43662</v>
+        <v>43663</v>
       </c>
       <c r="H27" t="n">
-        <v>1648.6</v>
+        <v>1651.95</v>
       </c>
       <c r="I27" t="n">
         <v>1649.740529354117</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.46</v>
+        <v>-3.67</v>
       </c>
       <c r="L27" t="n">
         <v>8.57</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>7.03</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43686</v>
+        <v>43690</v>
       </c>
       <c r="H28" t="n">
-        <v>1664.95</v>
+        <v>1524.4</v>
       </c>
       <c r="I28" t="n">
         <v>1547.927076247744</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K28" t="n">
-        <v>0.79</v>
+        <v>-7.72</v>
       </c>
       <c r="L28" t="n">
-        <v>5.25</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>0.93</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>1.49</v>
+        <v>8.44</v>
       </c>
       <c r="O28" t="n">
         <v>0.2</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>13.52</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43733</v>
+        <v>43734</v>
       </c>
       <c r="H29" t="n">
-        <v>1633.45</v>
+        <v>1675.05</v>
       </c>
       <c r="I29" t="n">
         <v>1673.342447129296</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.15</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>9.619999999999999</v>
+        <v>11.85</v>
       </c>
       <c r="M29" t="n">
         <v>0.86</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H30" t="n">
-        <v>2149.2</v>
+        <v>1912.85</v>
       </c>
       <c r="I30" t="n">
         <v>2033.689794251141</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K30" t="n">
-        <v>28.31</v>
+        <v>14.2</v>
       </c>
       <c r="L30" t="n">
         <v>4.78</v>
@@ -2151,7 +2510,7 @@
         <v>2.16</v>
       </c>
       <c r="N30" t="n">
-        <v>2.75</v>
+        <v>11</v>
       </c>
       <c r="O30" t="n">
         <v>2.55</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>18.72</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43929</v>
+        <v>43930</v>
       </c>
       <c r="H31" t="n">
-        <v>2168.95</v>
+        <v>2310.9</v>
       </c>
       <c r="I31" t="n">
         <v>2183.666143157368</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K31" t="n">
-        <v>-13.39</v>
+        <v>-20.81</v>
       </c>
       <c r="L31" t="n">
-        <v>15.77</v>
+        <v>29</v>
       </c>
       <c r="M31" t="n">
         <v>3.96</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>20.35</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44013</v>
+        <v>44014</v>
       </c>
       <c r="H32" t="n">
-        <v>2241.25</v>
+        <v>2196.65</v>
       </c>
       <c r="I32" t="n">
         <v>2203.19325020371</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.01</v>
+        <v>-4.94</v>
       </c>
       <c r="L32" t="n">
-        <v>4.79</v>
+        <v>9.56</v>
       </c>
       <c r="M32" t="n">
-        <v>4.58</v>
+        <v>6.3</v>
       </c>
       <c r="N32" t="n">
         <v>2.78</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44034</v>
+        <v>44035</v>
       </c>
       <c r="H33" t="n">
-        <v>2261.75</v>
+        <v>2397.45</v>
       </c>
       <c r="I33" t="n">
         <v>2380.961395837281</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.96</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>5.93</v>
+        <v>9.66</v>
       </c>
       <c r="M33" t="n">
         <v>1.34</v>
       </c>
       <c r="N33" t="n">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
         <v>-1.99</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.23</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c r="H34" t="n">
-        <v>3644.8</v>
+        <v>3565.3</v>
       </c>
       <c r="I34" t="n">
         <v>3632.583096717997</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K34" t="n">
-        <v>52.03</v>
+        <v>48.71</v>
       </c>
       <c r="L34" t="n">
         <v>5.12</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>7</v>
+      </c>
+      <c r="U34" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44231</v>
+        <v>44232</v>
       </c>
       <c r="H35" t="n">
-        <v>3678.9</v>
+        <v>3822.45</v>
       </c>
       <c r="I35" t="n">
         <v>3682.753534064559</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.19</v>
+        <v>-7.21</v>
       </c>
       <c r="L35" t="n">
-        <v>4.47</v>
+        <v>8.26</v>
       </c>
       <c r="M35" t="n">
         <v>2.21</v>
       </c>
       <c r="N35" t="n">
-        <v>3.71</v>
+        <v>3.9</v>
       </c>
       <c r="O35" t="n">
         <v>-2.18</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>10.69</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44252</v>
+        <v>44253</v>
       </c>
       <c r="H36" t="n">
-        <v>3440.05</v>
+        <v>3363.1</v>
       </c>
       <c r="I36" t="n">
         <v>3413.918742170219</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K36" t="n">
-        <v>-10</v>
+        <v>-12.02</v>
       </c>
       <c r="L36" t="n">
-        <v>10.73</v>
+        <v>12.98</v>
       </c>
       <c r="M36" t="n">
         <v>0.82</v>
       </c>
       <c r="N36" t="n">
-        <v>1.93</v>
+        <v>2.24</v>
       </c>
       <c r="O36" t="n">
         <v>3.9</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>10.3</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44285</v>
+        <v>44286</v>
       </c>
       <c r="H37" t="n">
-        <v>3584.25</v>
+        <v>3622.8</v>
       </c>
       <c r="I37" t="n">
         <v>3600.861143520318</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.58</v>
+        <v>-7.72</v>
       </c>
       <c r="L37" t="n">
-        <v>7.04</v>
+        <v>8.25</v>
       </c>
       <c r="M37" t="n">
         <v>1.71</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44466</v>
+        <v>44467</v>
       </c>
       <c r="H38" t="n">
-        <v>4932.55</v>
+        <v>4784.05</v>
       </c>
       <c r="I38" t="n">
         <v>4905.318109309424</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K38" t="n">
-        <v>36.15</v>
+        <v>32.05</v>
       </c>
       <c r="L38" t="n">
         <v>1.69</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>9.23</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44470</v>
+        <v>44473</v>
       </c>
       <c r="H39" t="n">
-        <v>4832.3</v>
+        <v>5220.7</v>
       </c>
       <c r="I39" t="n">
         <v>5190.96467784235</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.01</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>3.78</v>
+        <v>11.11</v>
       </c>
       <c r="M39" t="n">
-        <v>0.66</v>
+        <v>1.19</v>
       </c>
       <c r="N39" t="n">
-        <v>0.7</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="O39" t="n">
         <v>-3.01</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>11.51</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44504</v>
+        <v>44508</v>
       </c>
       <c r="H40" t="n">
-        <v>5208.05</v>
+        <v>4896.7</v>
       </c>
       <c r="I40" t="n">
         <v>4939.595557927718</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.24</v>
+        <v>-6.21</v>
       </c>
       <c r="L40" t="n">
-        <v>6.62</v>
+        <v>9.06</v>
       </c>
       <c r="M40" t="n">
-        <v>0.42</v>
+        <v>3.55</v>
       </c>
       <c r="N40" t="n">
-        <v>2.83</v>
+        <v>5.98</v>
       </c>
       <c r="O40" t="n">
         <v>8.039999999999999</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>10.51</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44607</v>
+        <v>44608</v>
       </c>
       <c r="H41" t="n">
-        <v>4325.8</v>
+        <v>4465.15</v>
       </c>
       <c r="I41" t="n">
         <v>4413.134324469202</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K41" t="n">
-        <v>11.66</v>
+        <v>8.81</v>
       </c>
       <c r="L41" t="n">
         <v>4.01</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>10.45</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H42" t="n">
-        <v>4181.6</v>
+        <v>3936.65</v>
       </c>
       <c r="I42" t="n">
         <v>4078.26558549755</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.35</v>
+        <v>-11.84</v>
       </c>
       <c r="L42" t="n">
-        <v>7.38</v>
+        <v>12.29</v>
       </c>
       <c r="M42" t="n">
         <v>2.54</v>
       </c>
       <c r="N42" t="n">
-        <v>2.18</v>
+        <v>5.86</v>
       </c>
       <c r="O42" t="n">
         <v>3.22</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>12.65</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H43" t="n">
-        <v>4402.25</v>
+        <v>4504.35</v>
       </c>
       <c r="I43" t="n">
         <v>4434.535272169552</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>-11.83</v>
+        <v>-14.42</v>
       </c>
       <c r="L43" t="n">
-        <v>13.76</v>
+        <v>14.82</v>
       </c>
       <c r="M43" t="n">
         <v>2.88</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>8.6</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H44" t="n">
-        <v>4365.8</v>
+        <v>4165.85</v>
       </c>
       <c r="I44" t="n">
         <v>4218.406652301981</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.08</v>
+        <v>-7.51</v>
       </c>
       <c r="L44" t="n">
-        <v>3.87</v>
+        <v>8.5</v>
       </c>
       <c r="M44" t="n">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="N44" t="n">
-        <v>3.67</v>
+        <v>4.58</v>
       </c>
       <c r="O44" t="n">
         <v>2.32</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.42</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44763</v>
+        <v>44764</v>
       </c>
       <c r="H45" t="n">
-        <v>3794.5</v>
+        <v>3796.75</v>
       </c>
       <c r="I45" t="n">
         <v>3795.277537789716</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K45" t="n">
-        <v>8.91</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L45" t="n">
         <v>6.55</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.97</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44791</v>
+        <v>44792</v>
       </c>
       <c r="H46" t="n">
-        <v>3743.6</v>
+        <v>3696.2</v>
       </c>
       <c r="I46" t="n">
         <v>3715.232097202959</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.4</v>
+        <v>-2.65</v>
       </c>
       <c r="L46" t="n">
         <v>3.42</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.2</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44837</v>
+        <v>44838</v>
       </c>
       <c r="H47" t="n">
-        <v>3726.85</v>
+        <v>3780.1</v>
       </c>
       <c r="I47" t="n">
         <v>3758.822934932409</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.83</v>
+        <v>-2.27</v>
       </c>
       <c r="L47" t="n">
         <v>2.73</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>6.65</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44844</v>
+        <v>44845</v>
       </c>
       <c r="H48" t="n">
-        <v>3686.6</v>
+        <v>3502.2</v>
       </c>
       <c r="I48" t="n">
         <v>3528.59412800395</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.47</v>
+        <v>-7.35</v>
       </c>
       <c r="L48" t="n">
-        <v>3.44</v>
+        <v>7.67</v>
       </c>
       <c r="M48" t="n">
         <v>1.42</v>
       </c>
       <c r="N48" t="n">
-        <v>1.32</v>
+        <v>5</v>
       </c>
       <c r="O48" t="n">
         <v>1.43</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>10.68</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44865</v>
+        <v>44866</v>
       </c>
       <c r="H49" t="n">
-        <v>3608.9</v>
+        <v>3836.45</v>
       </c>
       <c r="I49" t="n">
         <v>3777.421830854947</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.05</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>5.79</v>
+        <v>9.94</v>
       </c>
       <c r="M49" t="n">
         <v>1.64</v>
       </c>
       <c r="N49" t="n">
-        <v>1.73</v>
+        <v>6.31</v>
       </c>
       <c r="O49" t="n">
         <v>-5</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>9.73</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44869</v>
+        <v>44872</v>
       </c>
       <c r="H50" t="n">
-        <v>3746.3</v>
+        <v>3414.55</v>
       </c>
       <c r="I50" t="n">
         <v>3556.454627353841</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.35</v>
+        <v>-11</v>
       </c>
       <c r="L50" t="n">
-        <v>5.77</v>
+        <v>11.25</v>
       </c>
       <c r="M50" t="n">
         <v>-0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.43</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="O50" t="n">
         <v>6.31</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>15.41</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H51" t="n">
-        <v>3351.55</v>
+        <v>3518.75</v>
       </c>
       <c r="I51" t="n">
         <v>3455.14076312736</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K51" t="n">
-        <v>1.85</v>
+        <v>-3.05</v>
       </c>
       <c r="L51" t="n">
         <v>10.46</v>
@@ -3348,7 +3959,7 @@
         <v>0.86</v>
       </c>
       <c r="N51" t="n">
-        <v>1.98</v>
+        <v>4.99</v>
       </c>
       <c r="O51" t="n">
         <v>-8.859999999999999</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44937</v>
+        <v>44938</v>
       </c>
       <c r="H52" t="n">
-        <v>3411.45</v>
+        <v>3305.3</v>
       </c>
       <c r="I52" t="n">
         <v>3322.885137303256</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.05</v>
+        <v>-6.07</v>
       </c>
       <c r="L52" t="n">
-        <v>4.75</v>
+        <v>6.75</v>
       </c>
       <c r="M52" t="n">
         <v>0.2</v>
       </c>
       <c r="N52" t="n">
-        <v>2.58</v>
+        <v>3.11</v>
       </c>
       <c r="O52" t="n">
         <v>4.99</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.75</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45027</v>
+        <v>45028</v>
       </c>
       <c r="H53" t="n">
-        <v>2927.35</v>
+        <v>3212.1</v>
       </c>
       <c r="I53" t="n">
         <v>2938.677728863729</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K53" t="n">
-        <v>11.43</v>
+        <v>2.82</v>
       </c>
       <c r="L53" t="n">
         <v>3.67</v>
@@ -3462,7 +4097,7 @@
         <v>1.22</v>
       </c>
       <c r="N53" t="n">
-        <v>2.5</v>
+        <v>9.73</v>
       </c>
       <c r="O53" t="n">
         <v>-3.11</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.83</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45063</v>
+        <v>45064</v>
       </c>
       <c r="H54" t="n">
-        <v>3268</v>
+        <v>3153.5</v>
       </c>
       <c r="I54" t="n">
         <v>3183.459744202469</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K54" t="n">
-        <v>1.74</v>
+        <v>-1.82</v>
       </c>
       <c r="L54" t="n">
         <v>8.44</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>10.31</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45068</v>
+        <v>45069</v>
       </c>
       <c r="H55" t="n">
-        <v>3265</v>
+        <v>3385.8</v>
       </c>
       <c r="I55" t="n">
         <v>3381.593831208166</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.54</v>
+        <v>-7.37</v>
       </c>
       <c r="L55" t="n">
-        <v>4.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M55" t="n">
         <v>0.49</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>11.69</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45168</v>
+        <v>45169</v>
       </c>
       <c r="H56" t="n">
-        <v>3630.8</v>
+        <v>3592.1</v>
       </c>
       <c r="I56" t="n">
         <v>3613.856745439037</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K56" t="n">
-        <v>7.24</v>
+        <v>6.09</v>
       </c>
       <c r="L56" t="n">
         <v>4.87</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>6.58</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45180</v>
+        <v>45181</v>
       </c>
       <c r="H57" t="n">
-        <v>3736.25</v>
+        <v>3787.8</v>
       </c>
       <c r="I57" t="n">
         <v>3777.039704327436</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.01</v>
+        <v>-5.45</v>
       </c>
       <c r="L57" t="n">
-        <v>4.37</v>
+        <v>7.12</v>
       </c>
       <c r="M57" t="n">
         <v>0.39</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>5.65</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45218</v>
+        <v>45219</v>
       </c>
       <c r="H58" t="n">
-        <v>3637.75</v>
+        <v>3554.3</v>
       </c>
       <c r="I58" t="n">
         <v>3616.469614505382</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.96</v>
+        <v>-6.16</v>
       </c>
       <c r="L58" t="n">
-        <v>4.94</v>
+        <v>6.7</v>
       </c>
       <c r="M58" t="n">
         <v>1.15</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.77</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="H59" t="n">
-        <v>3548.25</v>
+        <v>3600.85</v>
       </c>
       <c r="I59" t="n">
         <v>3569.922953936934</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K59" t="n">
-        <v>0.17</v>
+        <v>-1.31</v>
       </c>
       <c r="L59" t="n">
         <v>2.25</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.24</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="H60" t="n">
-        <v>3814.5</v>
+        <v>3728.8</v>
       </c>
       <c r="I60" t="n">
         <v>3780.115555076038</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K60" t="n">
-        <v>5.93</v>
+        <v>3.55</v>
       </c>
       <c r="L60" t="n">
         <v>1.41</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.48</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H61" t="n">
-        <v>3567.95</v>
+        <v>3622.5</v>
       </c>
       <c r="I61" t="n">
         <v>3582.739809518544</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K61" t="n">
-        <v>4.31</v>
+        <v>2.85</v>
       </c>
       <c r="L61" t="n">
         <v>2.79</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.33</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="H62" t="n">
-        <v>5849.45</v>
+        <v>5782.35</v>
       </c>
       <c r="I62" t="n">
         <v>5801.619039667886</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K62" t="n">
-        <v>61.48</v>
+        <v>59.62</v>
       </c>
       <c r="L62" t="n">
         <v>1.86</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>9</v>
+      </c>
+      <c r="U62" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>7.87</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45691</v>
+        <v>45692</v>
       </c>
       <c r="H63" t="n">
-        <v>5884.1</v>
+        <v>6096.25</v>
       </c>
       <c r="I63" t="n">
         <v>5996.297561870337</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.76</v>
+        <v>-5.43</v>
       </c>
       <c r="L63" t="n">
         <v>8.07</v>
       </c>
       <c r="M63" t="n">
-        <v>0.91</v>
+        <v>2.82</v>
       </c>
       <c r="N63" t="n">
         <v>4.73</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>11.11</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="H64" t="n">
-        <v>5615.8</v>
+        <v>5480.25</v>
       </c>
       <c r="I64" t="n">
         <v>5521.643504551112</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.88</v>
+        <v>-10.1</v>
       </c>
       <c r="L64" t="n">
-        <v>8.48</v>
+        <v>12</v>
       </c>
       <c r="M64" t="n">
         <v>1.33</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.59</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H65" t="n">
-        <v>5640</v>
+        <v>5891.5</v>
       </c>
       <c r="I65" t="n">
         <v>5840.913286937242</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.92</v>
+        <v>-7.5</v>
       </c>
       <c r="L65" t="n">
         <v>8.94</v>
@@ -4146,7 +4925,7 @@
         <v>3.95</v>
       </c>
       <c r="N65" t="n">
-        <v>3.77</v>
+        <v>4.46</v>
       </c>
       <c r="O65" t="n">
         <v>-2.41</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>11.58</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="H66" t="n">
-        <v>6688</v>
+        <v>6613</v>
       </c>
       <c r="I66" t="n">
         <v>6618.464298266284</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K66" t="n">
-        <v>13.52</v>
+        <v>12.25</v>
       </c>
       <c r="L66" t="n">
         <v>1.57</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.75</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="H67" t="n">
-        <v>5826.5</v>
+        <v>6104.5</v>
       </c>
       <c r="I67" t="n">
         <v>6061.242243349377</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K67" t="n">
-        <v>11.89</v>
+        <v>7.69</v>
       </c>
       <c r="L67" t="n">
         <v>1.82</v>
@@ -4260,7 +5063,7 @@
         <v>1.68</v>
       </c>
       <c r="N67" t="n">
-        <v>2.73</v>
+        <v>4.77</v>
       </c>
       <c r="O67" t="n">
         <v>-1.12</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="H68" t="n">
-        <v>6462.5</v>
+        <v>6373</v>
       </c>
       <c r="I68" t="n">
         <v>6434.092917710274</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K68" t="n">
-        <v>5.86</v>
+        <v>4.4</v>
       </c>
       <c r="L68" t="n">
         <v>4.47</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.41</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="H69" t="n">
-        <v>6395.5</v>
+        <v>6474</v>
       </c>
       <c r="I69" t="n">
         <v>6438.123068487514</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.35</v>
+        <v>-1.58</v>
       </c>
       <c r="L69" t="n">
         <v>6.59</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.74</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="H70" t="n">
-        <v>6140</v>
+        <v>5972.5</v>
       </c>
       <c r="I70" t="n">
         <v>5972.999410859278</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K70" t="n">
-        <v>-5.16</v>
+        <v>-7.75</v>
       </c>
       <c r="L70" t="n">
         <v>8.449999999999999</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>8.82</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="H71" t="n">
-        <v>6177.5</v>
+        <v>6293.5</v>
       </c>
       <c r="I71" t="n">
         <v>6266.585483644551</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.43</v>
+        <v>-5.37</v>
       </c>
       <c r="L71" t="n">
-        <v>3.54</v>
+        <v>5.7</v>
       </c>
       <c r="M71" t="n">
         <v>1.3</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8.25</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H72" t="n">
-        <v>9285</v>
+        <v>9023</v>
       </c>
       <c r="I72" t="n">
         <v>9033.911249416495</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K72" t="n">
-        <v>47.53</v>
+        <v>43.37</v>
       </c>
       <c r="L72" t="n">
         <v>1.8</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>7</v>
+      </c>
+      <c r="U72" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>10</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9563,7 +10446,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="6">
@@ -9573,7 +10456,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -9583,7 +10466,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8">
@@ -9593,7 +10476,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -9603,7 +10486,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -9613,7 +10496,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -9653,7 +10536,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.82</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="15">
@@ -9663,7 +10546,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.34</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="16">
@@ -9673,7 +10556,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.17</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="17">
@@ -9683,7 +10566,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>61.48</v>
+        <v>59.62</v>
       </c>
     </row>
     <row r="18">
@@ -9693,7 +10576,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.1</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="19">
@@ -9703,7 +10586,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.63</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="20">
@@ -9713,7 +10596,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.87</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="21">
@@ -9723,7 +10606,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.77</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
@@ -9733,7 +10616,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -9743,7 +10626,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -9753,7 +10636,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="25">
@@ -9763,7 +10646,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -9773,7 +10656,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.49</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="27">
@@ -9783,7 +10666,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.39</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="28">
@@ -9793,7 +10676,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
